--- a/data/gravel/Chumba Yaupon Ti Rigid 2025.xlsx
+++ b/data/gravel/Chumba Yaupon Ti Rigid 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{007707E6-318E-4044-ADF0-41578D5FF53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2074D96-08C1-EB4F-AC96-088EEC21E5C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1700" yWindow="500" windowWidth="25400" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="136">
   <si>
     <t>brand</t>
   </si>
@@ -353,12 +353,6 @@
     <t>optional</t>
   </si>
   <si>
-    <t>trail</t>
-  </si>
-  <si>
-    <t>a8:h31</t>
-  </si>
-  <si>
     <t>class</t>
   </si>
   <si>
@@ -438,6 +432,15 @@
   </si>
   <si>
     <t>Enve Mtn Boost Carbon</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>a8:h32</t>
   </si>
 </sst>
 </file>
@@ -792,7 +795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P78"/>
+  <dimension ref="A1:P79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -811,7 +814,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
@@ -835,12 +838,12 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
@@ -848,7 +851,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>107</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="24" x14ac:dyDescent="0.3">
@@ -1199,22 +1202,22 @@
         <v>1169</v>
       </c>
       <c r="I16" t="s">
+        <v>126</v>
+      </c>
+      <c r="J16" t="s">
+        <v>127</v>
+      </c>
+      <c r="K16" t="s">
         <v>128</v>
       </c>
-      <c r="J16" t="s">
+      <c r="L16" t="s">
         <v>129</v>
       </c>
-      <c r="K16" t="s">
+      <c r="M16" t="s">
         <v>130</v>
       </c>
-      <c r="L16" t="s">
+      <c r="N16" t="s">
         <v>131</v>
-      </c>
-      <c r="M16" t="s">
-        <v>132</v>
-      </c>
-      <c r="N16" t="s">
-        <v>133</v>
       </c>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
@@ -1341,7 +1344,7 @@
         <v>490</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
@@ -1383,7 +1386,25 @@
     </row>
     <row r="22" spans="1:16" ht="21" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>106</v>
+        <v>133</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
       </c>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
@@ -1393,516 +1414,535 @@
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>33</v>
-      </c>
+    <row r="23" spans="1:16" ht="21" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>35</v>
+      </c>
+      <c r="B26" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" t="s">
-        <v>37</v>
-      </c>
-      <c r="C27">
-        <v>29</v>
-      </c>
-      <c r="D27">
-        <v>29</v>
-      </c>
-      <c r="E27">
-        <v>29</v>
-      </c>
-      <c r="F27">
-        <v>29</v>
-      </c>
-      <c r="G27">
-        <v>29</v>
-      </c>
-      <c r="H27">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C28">
-        <v>2.4</v>
+        <v>29</v>
       </c>
       <c r="D28">
-        <v>2.4</v>
+        <v>29</v>
       </c>
       <c r="E28">
-        <v>2.4</v>
+        <v>29</v>
       </c>
       <c r="F28">
-        <v>2.4</v>
+        <v>29</v>
       </c>
       <c r="G28">
-        <v>2.4</v>
+        <v>29</v>
       </c>
       <c r="H28">
-        <v>2.4</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B29" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C29">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="D29">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="E29">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="F29">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="G29">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="H29">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30">
+        <v>2.6</v>
+      </c>
+      <c r="D30">
+        <v>2.6</v>
+      </c>
+      <c r="E30">
+        <v>2.6</v>
+      </c>
+      <c r="F30">
+        <v>2.6</v>
+      </c>
+      <c r="G30">
+        <v>2.6</v>
+      </c>
+      <c r="H30">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>40</v>
       </c>
-      <c r="C30">
-        <f>C32*2.54</f>
+      <c r="C31">
+        <f>C33*2.54</f>
         <v>162.56</v>
       </c>
-      <c r="D30">
-        <f t="shared" ref="D30:H31" si="3">D32*2.54</f>
+      <c r="D31">
+        <f t="shared" ref="D31:H32" si="3">D33*2.54</f>
         <v>170.18</v>
       </c>
-      <c r="E30">
+      <c r="E31">
         <f t="shared" si="3"/>
         <v>175.26</v>
       </c>
-      <c r="F30">
+      <c r="F31">
         <f t="shared" si="3"/>
         <v>180.34</v>
       </c>
-      <c r="G30">
+      <c r="G31">
         <f t="shared" si="3"/>
         <v>185.42000000000002</v>
       </c>
-      <c r="H30">
+      <c r="H31">
         <f t="shared" si="3"/>
         <v>187.96</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>41</v>
       </c>
-      <c r="C31">
-        <f>C33*2.54</f>
+      <c r="C32">
+        <f>C34*2.54</f>
         <v>167.64000000000001</v>
       </c>
-      <c r="D31">
+      <c r="D32">
         <f t="shared" si="3"/>
         <v>175.26</v>
       </c>
-      <c r="E31">
+      <c r="E32">
         <f t="shared" si="3"/>
         <v>177.8</v>
       </c>
-      <c r="F31">
+      <c r="F32">
         <f t="shared" si="3"/>
         <v>185.42000000000002</v>
       </c>
-      <c r="G31">
+      <c r="G32">
         <f t="shared" si="3"/>
         <v>187.96</v>
       </c>
-      <c r="H31">
+      <c r="H32">
         <f t="shared" si="3"/>
         <v>193.04</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C32">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C33">
         <v>64</v>
       </c>
-      <c r="D32">
+      <c r="D33">
         <v>67</v>
       </c>
-      <c r="E32">
+      <c r="E33">
         <v>69</v>
       </c>
-      <c r="F32">
+      <c r="F33">
         <v>71</v>
       </c>
-      <c r="G32">
+      <c r="G33">
         <v>73</v>
       </c>
-      <c r="H32">
+      <c r="H33">
         <v>74</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33">
-        <v>66</v>
-      </c>
-      <c r="D33">
-        <v>69</v>
-      </c>
-      <c r="E33">
-        <v>70</v>
-      </c>
-      <c r="F33">
-        <v>73</v>
-      </c>
-      <c r="G33">
-        <v>74</v>
-      </c>
-      <c r="H33">
-        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>108</v>
+        <v>42</v>
       </c>
       <c r="B34" t="s">
-        <v>109</v>
-      </c>
-      <c r="C34" t="s">
-        <v>87</v>
-      </c>
-      <c r="D34" t="s">
-        <v>88</v>
-      </c>
-      <c r="E34" t="s">
-        <v>89</v>
-      </c>
-      <c r="F34" t="s">
-        <v>90</v>
-      </c>
-      <c r="G34" t="s">
-        <v>91</v>
-      </c>
-      <c r="H34" t="s">
-        <v>92</v>
-      </c>
-      <c r="I34" t="s">
-        <v>86</v>
+        <v>43</v>
+      </c>
+      <c r="C34">
+        <v>66</v>
+      </c>
+      <c r="D34">
+        <v>69</v>
+      </c>
+      <c r="E34">
+        <v>70</v>
+      </c>
+      <c r="F34">
+        <v>73</v>
+      </c>
+      <c r="G34">
+        <v>74</v>
+      </c>
+      <c r="H34">
+        <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B35" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C35" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D35" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E35" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="F35" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G35" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="H35" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="I35" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>112</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>113</v>
+        <v>108</v>
+      </c>
+      <c r="B36" t="s">
+        <v>109</v>
       </c>
       <c r="C36" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D36" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E36" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F36" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G36" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H36" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I36" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>123</v>
+        <v>111</v>
+      </c>
+      <c r="C37" t="s">
+        <v>99</v>
+      </c>
+      <c r="D37" t="s">
+        <v>99</v>
+      </c>
+      <c r="E37" t="s">
+        <v>99</v>
+      </c>
+      <c r="F37" t="s">
+        <v>99</v>
+      </c>
+      <c r="G37" t="s">
+        <v>94</v>
+      </c>
+      <c r="H37" t="s">
+        <v>100</v>
+      </c>
+      <c r="I37" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>46</v>
-      </c>
-      <c r="B39">
-        <v>20</v>
+        <v>45</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40">
-        <v>2.6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>48</v>
+        <v>47</v>
+      </c>
+      <c r="B41">
+        <v>2.6</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>49</v>
-      </c>
-      <c r="B42">
-        <v>120</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>50</v>
-      </c>
-      <c r="B43" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="B43">
+        <v>120</v>
+      </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>51</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="B44" s="1"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>53</v>
-      </c>
-      <c r="B46">
-        <v>148</v>
+        <v>52</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B47">
-        <v>110</v>
+        <v>148</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>117</v>
+        <v>54</v>
+      </c>
+      <c r="B48">
+        <v>110</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>55</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>57</v>
-      </c>
-      <c r="B56">
-        <v>31.6</v>
+        <v>56</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>58</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>102</v>
+        <v>57</v>
+      </c>
+      <c r="B57">
+        <v>31.6</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>59</v>
-      </c>
-      <c r="B58">
-        <v>38</v>
+        <v>58</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>60</v>
+        <v>59</v>
+      </c>
+      <c r="B59">
+        <v>38</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>64</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>104</v>
+        <v>63</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>66</v>
+        <v>65</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>68</v>
-      </c>
-      <c r="B67">
-        <v>3</v>
+        <v>67</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B68">
-        <v>1</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>105</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>70</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>79</v>
+        <v>69</v>
+      </c>
+      <c r="B69">
+        <v>1</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>105</v>
@@ -1910,59 +1950,70 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>71</v>
+        <v>70</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>75</v>
-      </c>
-      <c r="B74">
-        <v>1695</v>
+        <v>74</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>76</v>
+        <v>75</v>
+      </c>
+      <c r="B75">
+        <v>1695</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>77</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>115</v>
-      </c>
-      <c r="B78" t="s">
-        <v>116</v>
+        <v>78</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>113</v>
+      </c>
+      <c r="B79" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
